--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10513,6 +10513,229 @@
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128635312</v>
+      </c>
+      <c r="B94" t="n">
+        <v>90955</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>481081</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6784713</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128635352</v>
+      </c>
+      <c r="B95" t="n">
+        <v>92759</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>481010</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6784594</v>
+      </c>
+      <c r="S95" t="n">
+        <v>9</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92759</v>
+        <v>92764</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92764</v>
+        <v>92770</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92822</v>
+        <v>92827</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>91022</v>
+        <v>91028</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92827</v>
+        <v>92835</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -10518,7 +10518,7 @@
         <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>91028</v>
+        <v>91032</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>128635352</v>
       </c>
       <c r="B95" t="n">
-        <v>92835</v>
+        <v>92842</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119683440</v>
+        <v>119787002</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481045</v>
+        <v>481114</v>
       </c>
       <c r="R2" t="n">
-        <v>6784589</v>
+        <v>6784523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119683370</v>
+        <v>119683447</v>
       </c>
       <c r="B3" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,43 +783,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481038</v>
+        <v>481045</v>
       </c>
       <c r="R3" t="n">
-        <v>6784595</v>
+        <v>6784589</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,7 +844,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +854,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -920,19 +882,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119683447</v>
+        <v>119706842</v>
       </c>
       <c r="B4" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -954,18 +911,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481045</v>
+        <v>481041</v>
       </c>
       <c r="R4" t="n">
-        <v>6784589</v>
+        <v>6784511</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,22 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,68 +976,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119683503</v>
+        <v>119706849</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481058</v>
+        <v>481066</v>
       </c>
       <c r="R5" t="n">
-        <v>6784561</v>
+        <v>6784502</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,22 +1077,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119683489</v>
+        <v>119706885</v>
       </c>
       <c r="B6" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,36 +1095,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481045</v>
+        <v>481077</v>
       </c>
       <c r="R6" t="n">
-        <v>6784589</v>
+        <v>6784510</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1231,22 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,22 +1178,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119707034</v>
+        <v>119706915</v>
       </c>
       <c r="B7" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,28 +1196,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1321,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480988</v>
+        <v>481115</v>
       </c>
       <c r="R7" t="n">
-        <v>6784561</v>
+        <v>6784610</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,11 +1259,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>och troligen 2 gamla också</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,19 +1286,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119706915</v>
+        <v>119706931</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1432,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481115</v>
+        <v>481112</v>
       </c>
       <c r="R8" t="n">
-        <v>6784610</v>
+        <v>6784721</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1495,56 +1387,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119706846</v>
+        <v>119786882</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481066</v>
+        <v>481048</v>
       </c>
       <c r="R9" t="n">
-        <v>6784528</v>
+        <v>6784513</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,12 +1452,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,38 +1466,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119706842</v>
+        <v>119787028</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1635,22 +1513,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481041</v>
+        <v>481150</v>
       </c>
       <c r="R10" t="n">
-        <v>6784511</v>
+        <v>6784524</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,12 +1549,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,75 +1563,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119706939</v>
+        <v>119787115</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481111</v>
+        <v>481178</v>
       </c>
       <c r="R11" t="n">
-        <v>6784709</v>
+        <v>6784510</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,12 +1646,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,38 +1660,32 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119706849</v>
+        <v>119787167</v>
       </c>
       <c r="B12" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1847,22 +1707,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481066</v>
+        <v>481197</v>
       </c>
       <c r="R12" t="n">
-        <v>6784502</v>
+        <v>6784509</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,12 +1743,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,75 +1757,66 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119706890</v>
+        <v>119787665</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481078</v>
+        <v>481287</v>
       </c>
       <c r="R13" t="n">
-        <v>6784518</v>
+        <v>6784633</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,12 +1840,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,79 +1854,66 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119706984</v>
+        <v>119787770</v>
       </c>
       <c r="B14" t="n">
-        <v>90067</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481148</v>
+        <v>481267</v>
       </c>
       <c r="R14" t="n">
-        <v>6784737</v>
+        <v>6784656</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2102,12 +1937,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,7 +1961,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2128,63 +1972,55 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119706847</v>
+        <v>119787807</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481062</v>
+        <v>481250</v>
       </c>
       <c r="R15" t="n">
-        <v>6784508</v>
+        <v>6784659</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2208,12 +2044,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,7 +2068,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2234,22 +2079,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119707027</v>
+        <v>119787861</v>
       </c>
       <c r="B16" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,44 +2097,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480985</v>
+        <v>481216</v>
       </c>
       <c r="R16" t="n">
-        <v>6784560</v>
+        <v>6784655</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,12 +2160,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,7 +2184,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2344,26 +2195,21 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119706885</v>
+        <v>119788033</v>
       </c>
       <c r="B17" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2385,22 +2231,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481077</v>
+        <v>481181</v>
       </c>
       <c r="R17" t="n">
-        <v>6784510</v>
+        <v>6784644</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,12 +2267,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,75 +2281,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119706877</v>
+        <v>119788082</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481065</v>
+        <v>481144</v>
       </c>
       <c r="R18" t="n">
-        <v>6784504</v>
+        <v>6784602</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,12 +2364,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,75 +2378,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119706728</v>
+        <v>119788715</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480980</v>
+        <v>481104</v>
       </c>
       <c r="R19" t="n">
-        <v>6784536</v>
+        <v>6784681</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,12 +2461,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,7 +2485,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2662,63 +2496,55 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119706918</v>
+        <v>119788776</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481159</v>
+        <v>481179</v>
       </c>
       <c r="R20" t="n">
-        <v>6784628</v>
+        <v>6784744</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2742,12 +2568,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,75 +2582,66 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119706873</v>
+        <v>119788935</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481067</v>
+        <v>480987</v>
       </c>
       <c r="R21" t="n">
-        <v>6784504</v>
+        <v>6784663</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2848,12 +2665,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,75 +2679,66 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119706923</v>
+        <v>119789001</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481092</v>
+        <v>481138</v>
       </c>
       <c r="R22" t="n">
-        <v>6784685</v>
+        <v>6784747</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2954,12 +2762,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,75 +2776,66 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706741</v>
+        <v>119789066</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481017</v>
+        <v>480996</v>
       </c>
       <c r="R23" t="n">
-        <v>6784518</v>
+        <v>6784667</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3060,12 +2859,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,7 +2883,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3086,22 +2894,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706870</v>
+        <v>119789105</v>
       </c>
       <c r="B24" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,44 +2912,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481067</v>
+        <v>481038</v>
       </c>
       <c r="R24" t="n">
-        <v>6784504</v>
+        <v>6784721</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3170,12 +2966,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3184,38 +2980,32 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119706931</v>
+        <v>128635352</v>
       </c>
       <c r="B25" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3237,22 +3027,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481112</v>
+        <v>481010</v>
       </c>
       <c r="R25" t="n">
-        <v>6784721</v>
+        <v>6784594</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3276,12 +3063,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,7 +3087,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3302,60 +3098,55 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119741440</v>
+        <v>119787325</v>
       </c>
       <c r="B26" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>3690</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481034</v>
+        <v>481288</v>
       </c>
       <c r="R26" t="n">
-        <v>6784535</v>
+        <v>6784474</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3379,22 +3170,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3409,65 +3190,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Sebastian Kirppu, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119741905</v>
+        <v>119788846</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481034</v>
+        <v>481139</v>
       </c>
       <c r="R27" t="n">
-        <v>6784535</v>
+        <v>6784744</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3491,22 +3267,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,27 +3287,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119787665</v>
+        <v>119787790</v>
       </c>
       <c r="B28" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,21 +3310,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3573,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481287</v>
+        <v>481260</v>
       </c>
       <c r="R28" t="n">
-        <v>6784633</v>
+        <v>6784612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,50 +3396,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788483</v>
+        <v>119683440</v>
       </c>
       <c r="B29" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481050</v>
+        <v>481045</v>
       </c>
       <c r="R29" t="n">
-        <v>6784604</v>
+        <v>6784589</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,22 +3472,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,6 +3496,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3740,26 +3508,21 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119787827</v>
+        <v>119683503</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3780,20 +3543,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481229</v>
+        <v>481058</v>
       </c>
       <c r="R30" t="n">
-        <v>6784643</v>
+        <v>6784561</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3817,12 +3591,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,37 +3615,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788514</v>
+        <v>119706741</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3883,19 +3663,22 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481088</v>
+        <v>481017</v>
       </c>
       <c r="R31" t="n">
-        <v>6784614</v>
+        <v>6784518</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3919,12 +3702,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3933,33 +3716,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119787167</v>
+        <v>119706918</v>
       </c>
       <c r="B32" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,37 +3746,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481197</v>
+        <v>481159</v>
       </c>
       <c r="R32" t="n">
-        <v>6784509</v>
+        <v>6784628</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4021,12 +3803,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4035,33 +3817,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119788935</v>
+        <v>119741905</v>
       </c>
       <c r="B33" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,37 +3847,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480987</v>
+        <v>481034</v>
       </c>
       <c r="R33" t="n">
-        <v>6784663</v>
+        <v>6784535</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4123,12 +3901,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4143,27 +3931,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119789434</v>
+        <v>119786992</v>
       </c>
       <c r="B34" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4171,39 +3954,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481002</v>
+        <v>481048</v>
       </c>
       <c r="R34" t="n">
-        <v>6784693</v>
+        <v>6784513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,19 +4011,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,27 +4028,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119787115</v>
+        <v>119787094</v>
       </c>
       <c r="B35" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4288,21 +4051,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4312,10 +4075,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481178</v>
+        <v>481175</v>
       </c>
       <c r="R35" t="n">
-        <v>6784510</v>
+        <v>6784516</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,15 +4137,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119787831</v>
+        <v>119787740</v>
       </c>
       <c r="B36" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,34 +4148,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481250</v>
+        <v>481276</v>
       </c>
       <c r="R36" t="n">
-        <v>6784659</v>
+        <v>6784646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4447,19 +4205,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4474,27 +4222,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119788715</v>
+        <v>119787827</v>
       </c>
       <c r="B37" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4502,34 +4245,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481104</v>
+        <v>481229</v>
       </c>
       <c r="R37" t="n">
-        <v>6784681</v>
+        <v>6784643</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,19 +4302,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,27 +4319,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119787644</v>
+        <v>119787842</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,34 +4342,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481277</v>
+        <v>481216</v>
       </c>
       <c r="R38" t="n">
-        <v>6784621</v>
+        <v>6784655</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,9 +4399,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4688,27 +4426,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119788928</v>
+        <v>119787848</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,21 +4449,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4740,10 +4473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481138</v>
+        <v>481187</v>
       </c>
       <c r="R39" t="n">
-        <v>6784747</v>
+        <v>6784640</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,31 +4523,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119789016</v>
+        <v>119788094</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4842,10 +4570,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480995</v>
+        <v>481132</v>
       </c>
       <c r="R40" t="n">
-        <v>6784692</v>
+        <v>6784594</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4892,31 +4620,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119788094</v>
+        <v>119788514</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4944,10 +4667,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481132</v>
+        <v>481088</v>
       </c>
       <c r="R41" t="n">
-        <v>6784594</v>
+        <v>6784614</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,37 +4729,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119787470</v>
+        <v>119788519</v>
       </c>
       <c r="B42" t="n">
-        <v>91839</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5046,10 +4764,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481284</v>
+        <v>481087</v>
       </c>
       <c r="R42" t="n">
-        <v>6784549</v>
+        <v>6784724</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,15 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119789064</v>
+        <v>119788565</v>
       </c>
       <c r="B43" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5124,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5148,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481010</v>
+        <v>481108</v>
       </c>
       <c r="R43" t="n">
-        <v>6784679</v>
+        <v>6784708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5210,15 +4923,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119786882</v>
+        <v>119788662</v>
       </c>
       <c r="B44" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5226,21 +4934,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5250,10 +4958,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481048</v>
+        <v>481133</v>
       </c>
       <c r="R44" t="n">
-        <v>6784513</v>
+        <v>6784731</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5300,27 +5008,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119788782</v>
+        <v>119788851</v>
       </c>
       <c r="B45" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5328,43 +5031,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481195</v>
+        <v>481136</v>
       </c>
       <c r="R45" t="n">
-        <v>6784739</v>
+        <v>6784750</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5090,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5100,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5433,15 +5127,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788305</v>
+        <v>119788950</v>
       </c>
       <c r="B46" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5449,21 +5138,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5473,13 +5162,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481083</v>
+        <v>480996</v>
       </c>
       <c r="R46" t="n">
-        <v>6784643</v>
+        <v>6784667</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5508,7 +5197,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5518,7 +5207,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5545,15 +5234,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119788766</v>
+        <v>119789016</v>
       </c>
       <c r="B47" t="n">
-        <v>78543</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5245,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5269,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481176</v>
+        <v>480995</v>
       </c>
       <c r="R47" t="n">
-        <v>6784737</v>
+        <v>6784692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,31 +5319,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119788950</v>
+        <v>119789074</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5683,14 +5362,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480996</v>
+        <v>481031</v>
       </c>
       <c r="R48" t="n">
-        <v>6784667</v>
+        <v>6784712</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,19 +5399,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5747,67 +5416,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788574</v>
+        <v>119788774</v>
       </c>
       <c r="B49" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>4962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481104</v>
+        <v>481195</v>
       </c>
       <c r="R49" t="n">
-        <v>6784681</v>
+        <v>6784739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5839,7 +5498,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5849,7 +5508,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,15 +5535,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119787681</v>
+        <v>119788782</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5892,34 +5546,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481294</v>
+        <v>481195</v>
       </c>
       <c r="R50" t="n">
-        <v>6784626</v>
+        <v>6784739</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,9 +5612,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5966,49 +5639,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119788662</v>
+        <v>119787470</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6018,10 +5686,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481133</v>
+        <v>481284</v>
       </c>
       <c r="R51" t="n">
-        <v>6784731</v>
+        <v>6784549</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6080,53 +5748,55 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119788846</v>
+        <v>119792265</v>
       </c>
       <c r="B52" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90681</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>6268</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481139</v>
+        <v>481044</v>
       </c>
       <c r="R52" t="n">
-        <v>6784744</v>
+        <v>6784736</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6164,71 +5834,76 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119788851</v>
+        <v>119683370</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481136</v>
+        <v>481038</v>
       </c>
       <c r="R53" t="n">
-        <v>6784750</v>
+        <v>6784595</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6252,22 +5927,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6287,60 +5962,57 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119787770</v>
+        <v>119683489</v>
       </c>
       <c r="B54" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481267</v>
+        <v>481045</v>
       </c>
       <c r="R54" t="n">
-        <v>6784656</v>
+        <v>6784589</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6364,22 +6036,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6388,6 +6060,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6399,60 +6072,62 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119787139</v>
+        <v>119706870</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481215</v>
+        <v>481067</v>
       </c>
       <c r="R55" t="n">
-        <v>6784513</v>
+        <v>6784504</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6476,22 +6151,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6500,6 +6165,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6511,60 +6177,62 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119788571</v>
+        <v>119706902</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481088</v>
+        <v>481174</v>
       </c>
       <c r="R56" t="n">
-        <v>6784614</v>
+        <v>6784548</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6588,12 +6256,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6602,68 +6270,71 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119787744</v>
+        <v>119707027</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481267</v>
+        <v>480985</v>
       </c>
       <c r="R57" t="n">
-        <v>6784656</v>
+        <v>6784560</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6690,22 +6361,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6714,6 +6375,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6725,60 +6387,62 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119789074</v>
+        <v>119707034</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481031</v>
+        <v>480988</v>
       </c>
       <c r="R58" t="n">
-        <v>6784712</v>
+        <v>6784561</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6802,12 +6466,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>och troligen 2 gamla också</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6816,71 +6485,67 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119787759</v>
+        <v>119741440</v>
       </c>
       <c r="B59" t="n">
-        <v>79160</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481248</v>
+        <v>481034</v>
       </c>
       <c r="R59" t="n">
-        <v>6784628</v>
+        <v>6784535</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6904,12 +6569,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6924,49 +6599,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119788312</v>
+        <v>119788482</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6976,10 +6646,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481062</v>
+        <v>481092</v>
       </c>
       <c r="R60" t="n">
-        <v>6784614</v>
+        <v>6784610</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7026,62 +6696,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119787764</v>
+        <v>119788483</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481252</v>
+        <v>481050</v>
       </c>
       <c r="R61" t="n">
-        <v>6784627</v>
+        <v>6784604</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7111,9 +6776,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,65 +6803,63 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119786992</v>
+        <v>119706728</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481048</v>
+        <v>480980</v>
       </c>
       <c r="R62" t="n">
-        <v>6784513</v>
+        <v>6784536</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,12 +6883,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7224,71 +6897,70 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119787028</v>
+        <v>119706846</v>
       </c>
       <c r="B63" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481150</v>
+        <v>481066</v>
       </c>
       <c r="R63" t="n">
-        <v>6784524</v>
+        <v>6784528</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,12 +6984,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7326,71 +6998,70 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119789066</v>
+        <v>119706847</v>
       </c>
       <c r="B64" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480996</v>
+        <v>481062</v>
       </c>
       <c r="R64" t="n">
-        <v>6784667</v>
+        <v>6784508</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7414,22 +7085,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7438,6 +7099,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7449,26 +7111,21 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119787833</v>
+        <v>119706873</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7490,19 +7147,22 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481250</v>
+        <v>481067</v>
       </c>
       <c r="R65" t="n">
-        <v>6784659</v>
+        <v>6784504</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7526,22 +7186,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7550,6 +7200,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7561,60 +7212,58 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119787774</v>
+        <v>119706877</v>
       </c>
       <c r="B66" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481250</v>
+        <v>481065</v>
       </c>
       <c r="R66" t="n">
-        <v>6784627</v>
+        <v>6784504</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7638,12 +7287,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7652,71 +7301,70 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119788033</v>
+        <v>119706890</v>
       </c>
       <c r="B67" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481181</v>
+        <v>481078</v>
       </c>
       <c r="R67" t="n">
-        <v>6784644</v>
+        <v>6784518</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7740,12 +7388,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7754,80 +7402,70 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119787544</v>
+        <v>119706923</v>
       </c>
       <c r="B68" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481291</v>
+        <v>481092</v>
       </c>
       <c r="R68" t="n">
-        <v>6784590</v>
+        <v>6784685</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7851,22 +7489,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7887,60 +7515,58 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119788776</v>
+        <v>119706939</v>
       </c>
       <c r="B69" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481179</v>
+        <v>481111</v>
       </c>
       <c r="R69" t="n">
-        <v>6784744</v>
+        <v>6784709</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7964,12 +7590,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7978,55 +7604,51 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119789105</v>
+        <v>119786836</v>
       </c>
       <c r="B70" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8036,10 +7658,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481038</v>
+        <v>481049</v>
       </c>
       <c r="R70" t="n">
-        <v>6784721</v>
+        <v>6784514</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8098,19 +7720,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119786836</v>
+        <v>119787021</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -8138,10 +7755,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481049</v>
+        <v>481048</v>
       </c>
       <c r="R71" t="n">
-        <v>6784514</v>
+        <v>6784513</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8188,72 +7805,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119792265</v>
+        <v>119787139</v>
       </c>
       <c r="B72" t="n">
-        <v>89256</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6268</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481044</v>
+        <v>481215</v>
       </c>
       <c r="R72" t="n">
-        <v>6784736</v>
+        <v>6784513</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,18 +7885,27 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8310,19 +7924,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119787935</v>
+        <v>119787644</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -8350,10 +7959,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481160</v>
+        <v>481277</v>
       </c>
       <c r="R73" t="n">
-        <v>6784611</v>
+        <v>6784621</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8412,19 +8021,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119787771</v>
+        <v>119787681</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -8452,10 +8056,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481276</v>
+        <v>481294</v>
       </c>
       <c r="R74" t="n">
-        <v>6784646</v>
+        <v>6784626</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8502,27 +8106,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119788482</v>
+        <v>119787744</v>
       </c>
       <c r="B75" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8530,37 +8129,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6286</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481092</v>
+        <v>481267</v>
       </c>
       <c r="R75" t="n">
-        <v>6784610</v>
+        <v>6784656</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8587,9 +8186,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8604,49 +8213,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119787790</v>
+        <v>119787764</v>
       </c>
       <c r="B76" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8656,10 +8260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481260</v>
+        <v>481252</v>
       </c>
       <c r="R76" t="n">
-        <v>6784612</v>
+        <v>6784627</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8718,37 +8322,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119787715</v>
+        <v>119787771</v>
       </c>
       <c r="B77" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8758,10 +8357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481274</v>
+        <v>481276</v>
       </c>
       <c r="R77" t="n">
-        <v>6784652</v>
+        <v>6784646</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8808,31 +8407,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119787021</v>
+        <v>119787825</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8856,14 +8450,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481048</v>
+        <v>481250</v>
       </c>
       <c r="R78" t="n">
-        <v>6784513</v>
+        <v>6784659</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8893,9 +8487,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8910,62 +8514,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788083</v>
+        <v>119787935</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481216</v>
+        <v>481160</v>
       </c>
       <c r="R79" t="n">
-        <v>6784655</v>
+        <v>6784611</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8995,19 +8594,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9022,71 +8611,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788550</v>
+        <v>119788312</v>
       </c>
       <c r="B80" t="n">
-        <v>90084</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481050</v>
+        <v>481062</v>
       </c>
       <c r="R80" t="n">
-        <v>6784604</v>
+        <v>6784614</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9116,19 +8691,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9143,49 +8708,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119787002</v>
+        <v>119788560</v>
       </c>
       <c r="B81" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9195,10 +8755,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481114</v>
+        <v>481088</v>
       </c>
       <c r="R81" t="n">
-        <v>6784523</v>
+        <v>6784614</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9245,31 +8805,26 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119789077</v>
+        <v>119788786</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -9297,10 +8852,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481052</v>
+        <v>481176</v>
       </c>
       <c r="R82" t="n">
-        <v>6784759</v>
+        <v>6784737</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9359,59 +8914,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119787861</v>
+        <v>119788908</v>
       </c>
       <c r="B83" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481216</v>
+        <v>481028</v>
       </c>
       <c r="R83" t="n">
-        <v>6784655</v>
+        <v>6784697</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9441,19 +8982,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9468,49 +8999,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119789001</v>
+        <v>119788928</v>
       </c>
       <c r="B84" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9582,19 +9108,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788908</v>
+        <v>119789077</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -9622,10 +9143,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481028</v>
+        <v>481052</v>
       </c>
       <c r="R85" t="n">
-        <v>6784697</v>
+        <v>6784759</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,49 +9193,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119787848</v>
+        <v>119787759</v>
       </c>
       <c r="B86" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9724,10 +9240,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481187</v>
+        <v>481248</v>
       </c>
       <c r="R86" t="n">
-        <v>6784640</v>
+        <v>6784628</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9786,50 +9302,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119787094</v>
+        <v>119789434</v>
       </c>
       <c r="B87" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481175</v>
+        <v>481002</v>
       </c>
       <c r="R87" t="n">
-        <v>6784516</v>
+        <v>6784693</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9859,9 +9375,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9876,62 +9402,66 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119788082</v>
+        <v>119787544</v>
       </c>
       <c r="B88" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481144</v>
+        <v>481291</v>
       </c>
       <c r="R88" t="n">
-        <v>6784602</v>
+        <v>6784590</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9961,44 +9491,50 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119788519</v>
+        <v>119788104</v>
       </c>
       <c r="B89" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10006,34 +9542,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481087</v>
+        <v>481122</v>
       </c>
       <c r="R89" t="n">
-        <v>6784724</v>
+        <v>6784602</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10092,15 +9633,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119788104</v>
+        <v>119788574</v>
       </c>
       <c r="B90" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10133,14 +9669,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481122</v>
+        <v>481104</v>
       </c>
       <c r="R90" t="n">
-        <v>6784602</v>
+        <v>6784681</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10170,9 +9706,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10187,65 +9733,67 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119787740</v>
+        <v>119706984</v>
       </c>
       <c r="B91" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481276</v>
+        <v>481148</v>
       </c>
       <c r="R91" t="n">
-        <v>6784646</v>
+        <v>6784737</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10269,12 +9817,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10283,68 +9831,73 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119788565</v>
+        <v>119788550</v>
       </c>
       <c r="B92" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481108</v>
+        <v>481050</v>
       </c>
       <c r="R92" t="n">
-        <v>6784708</v>
+        <v>6784604</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10374,9 +9927,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10391,27 +9954,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119788774</v>
+        <v>128635312</v>
       </c>
       <c r="B93" t="n">
-        <v>88170</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10419,34 +9977,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4962</v>
+        <v>256703</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481195</v>
+        <v>481081</v>
       </c>
       <c r="R93" t="n">
-        <v>6784739</v>
+        <v>6784713</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10473,22 +10040,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10508,64 +10075,58 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128635312</v>
+        <v>119706843</v>
       </c>
       <c r="B94" t="n">
-        <v>91032</v>
+        <v>79350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>256703</v>
+        <v>260591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481081</v>
+        <v>481041</v>
       </c>
       <c r="R94" t="n">
-        <v>6784713</v>
+        <v>6784526</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10589,22 +10150,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10613,6 +10164,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10624,17 +10176,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128635352</v>
+        <v>119706891</v>
       </c>
       <c r="B95" t="n">
-        <v>92842</v>
+        <v>79350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10642,37 +10194,40 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2059</v>
+        <v>260591</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481010</v>
+        <v>481078</v>
       </c>
       <c r="R95" t="n">
-        <v>6784594</v>
+        <v>6784518</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10696,22 +10251,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10720,6 +10265,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10731,10 +10277,107 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>119787824</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Unnan, Unnan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>481276</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6784646</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788935</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128635352</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706741</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788950</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789016</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789074</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119707027</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119707034</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706728</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788908</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789434</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787002</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119683447</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706842</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706849</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706885</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2521,6 +2611,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706915</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2622,6 +2717,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706931</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786882</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2816,6 +2921,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787028</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2913,6 +3023,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787115</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3010,6 +3125,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787167</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3107,6 +3227,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787665</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3214,6 +3339,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787770</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3321,6 +3451,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787807</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3437,6 +3572,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787861</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3534,6 +3674,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3631,6 +3776,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788082</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3738,6 +3888,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788715</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3835,6 +3990,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788776</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3932,6 +4092,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789001</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4029,6 +4194,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789105</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4126,6 +4296,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787325</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4223,6 +4398,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788846</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4320,6 +4500,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787790</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4439,6 +4624,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119683440</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4558,6 +4748,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119683503</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4659,6 +4854,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706918</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4766,6 +4966,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119741905</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4863,6 +5068,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786992</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4960,6 +5170,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787094</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5057,6 +5272,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787740</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5154,6 +5374,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787827</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5261,6 +5486,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787842</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5358,6 +5588,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787848</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5455,6 +5690,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788094</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5552,6 +5792,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788514</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5649,6 +5894,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788519</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5746,6 +5996,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788565</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5843,6 +6098,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788662</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5950,6 +6210,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788851</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6057,6 +6322,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788774</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6173,6 +6443,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788782</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6270,6 +6545,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787470</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6375,6 +6655,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119792265</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6491,6 +6776,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119683370</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6601,6 +6891,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119683489</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6706,6 +7001,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706870</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6811,6 +7111,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706902</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6918,6 +7223,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119741440</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7015,6 +7325,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788482</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7122,6 +7437,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788483</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7223,6 +7543,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706846</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7324,6 +7649,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706847</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7425,6 +7755,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706873</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7526,6 +7861,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706877</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7627,6 +7967,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706890</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7728,6 +8073,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706923</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7829,6 +8179,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706939</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7926,6 +8281,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786836</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8023,6 +8383,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787021</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8130,6 +8495,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787139</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8227,6 +8597,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787644</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8324,6 +8699,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787681</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8431,6 +8811,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787744</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8528,6 +8913,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787764</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8625,6 +9015,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787771</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8732,6 +9127,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787825</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8829,6 +9229,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787935</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8926,6 +9331,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788312</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9023,6 +9433,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788560</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9120,6 +9535,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788786</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9217,6 +9637,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788928</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9314,6 +9739,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789077</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9411,6 +9841,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787759</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9528,6 +9963,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787544</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9630,6 +10070,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788104</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9742,6 +10187,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788574</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9847,6 +10297,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706984</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9963,6 +10418,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788550</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10079,6 +10539,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128635312</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10180,6 +10645,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706843</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10281,6 +10751,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706891</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10378,8 +10853,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787824</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ96"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1428,52 +1428,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119707027</v>
+        <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>90691</v>
+        <v>93363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480985</v>
+        <v>481009</v>
       </c>
       <c r="R9" t="n">
-        <v>6784560</v>
+        <v>6784557</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,12 +1493,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,7 +1517,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1526,19 +1528,19 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119707027</t>
+          <t>https://artportalen.se/Sighting/136128123</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119707034</v>
+        <v>119707027</v>
       </c>
       <c r="B10" t="n">
         <v>90691</v>
@@ -1580,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480988</v>
+        <v>480985</v>
       </c>
       <c r="R10" t="n">
-        <v>6784561</v>
+        <v>6784560</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1618,11 +1620,6 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>och troligen 2 gamla också</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1647,16 +1644,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119707034</t>
+          <t>https://artportalen.se/Sighting/119707027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119706728</v>
+        <v>119707034</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,24 +1661,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1691,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480980</v>
+        <v>480988</v>
       </c>
       <c r="R11" t="n">
-        <v>6784536</v>
+        <v>6784561</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1729,6 +1730,11 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>och troligen 2 gamla också</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1753,13 +1759,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706728</t>
+          <t>https://artportalen.se/Sighting/119707034</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119788908</v>
+        <v>119706728</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1788,19 +1794,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481028</v>
+        <v>480980</v>
       </c>
       <c r="R12" t="n">
-        <v>6784697</v>
+        <v>6784536</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,12 +1833,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,73 +1847,69 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788908</t>
+          <t>https://artportalen.se/Sighting/119706728</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119789434</v>
+        <v>119788908</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481002</v>
+        <v>481028</v>
       </c>
       <c r="R13" t="n">
-        <v>6784693</v>
+        <v>6784697</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,19 +1939,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,27 +1956,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119789434</t>
+          <t>https://artportalen.se/Sighting/119788908</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119787002</v>
+        <v>119789434</v>
       </c>
       <c r="B14" t="n">
-        <v>78993</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,34 +1984,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481114</v>
+        <v>481002</v>
       </c>
       <c r="R14" t="n">
-        <v>6784523</v>
+        <v>6784693</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,9 +2046,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,67 +2073,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787002</t>
+          <t>https://artportalen.se/Sighting/119789434</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119683447</v>
+        <v>119787002</v>
       </c>
       <c r="B15" t="n">
-        <v>93213</v>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481045</v>
+        <v>481114</v>
       </c>
       <c r="R15" t="n">
-        <v>6784589</v>
+        <v>6784523</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2147,22 +2155,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,31 +2169,30 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119683447</t>
+          <t>https://artportalen.se/Sighting/119787002</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706842</v>
+        <v>119683447</v>
       </c>
       <c r="B16" t="n">
         <v>93213</v>
@@ -2224,19 +2221,18 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481041</v>
+        <v>481045</v>
       </c>
       <c r="R16" t="n">
-        <v>6784511</v>
+        <v>6784589</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2263,12 +2259,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,19 +2295,19 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706842</t>
+          <t>https://artportalen.se/Sighting/119683447</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119706849</v>
+        <v>119706842</v>
       </c>
       <c r="B17" t="n">
         <v>93213</v>
@@ -2339,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481066</v>
+        <v>481041</v>
       </c>
       <c r="R17" t="n">
-        <v>6784502</v>
+        <v>6784511</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2401,13 +2407,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706849</t>
+          <t>https://artportalen.se/Sighting/119706842</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119706885</v>
+        <v>119706849</v>
       </c>
       <c r="B18" t="n">
         <v>93213</v>
@@ -2445,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481077</v>
+        <v>481066</v>
       </c>
       <c r="R18" t="n">
-        <v>6784510</v>
+        <v>6784502</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2507,13 +2513,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706885</t>
+          <t>https://artportalen.se/Sighting/119706849</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119706915</v>
+        <v>119706885</v>
       </c>
       <c r="B19" t="n">
         <v>93213</v>
@@ -2551,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481115</v>
+        <v>481077</v>
       </c>
       <c r="R19" t="n">
-        <v>6784610</v>
+        <v>6784510</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2613,13 +2619,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706915</t>
+          <t>https://artportalen.se/Sighting/119706885</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119706931</v>
+        <v>119706915</v>
       </c>
       <c r="B20" t="n">
         <v>93213</v>
@@ -2657,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481112</v>
+        <v>481115</v>
       </c>
       <c r="R20" t="n">
-        <v>6784721</v>
+        <v>6784610</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,13 +2725,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706931</t>
+          <t>https://artportalen.se/Sighting/119706915</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119786882</v>
+        <v>119706931</v>
       </c>
       <c r="B21" t="n">
         <v>93213</v>
@@ -2754,19 +2760,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481048</v>
+        <v>481112</v>
       </c>
       <c r="R21" t="n">
-        <v>6784513</v>
+        <v>6784721</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2790,12 +2799,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2804,30 +2813,31 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119786882</t>
+          <t>https://artportalen.se/Sighting/119706931</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119787028</v>
+        <v>119786882</v>
       </c>
       <c r="B22" t="n">
         <v>93213</v>
@@ -2862,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481150</v>
+        <v>481048</v>
       </c>
       <c r="R22" t="n">
-        <v>6784524</v>
+        <v>6784513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,24 +2922,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787028</t>
+          <t>https://artportalen.se/Sighting/119786882</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119787115</v>
+        <v>119787028</v>
       </c>
       <c r="B23" t="n">
         <v>93213</v>
@@ -2964,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481178</v>
+        <v>481150</v>
       </c>
       <c r="R23" t="n">
-        <v>6784510</v>
+        <v>6784524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,13 +3035,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787115</t>
+          <t>https://artportalen.se/Sighting/119787028</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119787167</v>
+        <v>119787115</v>
       </c>
       <c r="B24" t="n">
         <v>93213</v>
@@ -3066,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481197</v>
+        <v>481178</v>
       </c>
       <c r="R24" t="n">
-        <v>6784509</v>
+        <v>6784510</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,13 +3137,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787167</t>
+          <t>https://artportalen.se/Sighting/119787115</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119787665</v>
+        <v>119787167</v>
       </c>
       <c r="B25" t="n">
         <v>93213</v>
@@ -3168,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481287</v>
+        <v>481197</v>
       </c>
       <c r="R25" t="n">
-        <v>6784633</v>
+        <v>6784509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,13 +3239,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787665</t>
+          <t>https://artportalen.se/Sighting/119787167</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119787770</v>
+        <v>119787665</v>
       </c>
       <c r="B26" t="n">
         <v>93213</v>
@@ -3266,14 +3276,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481267</v>
+        <v>481287</v>
       </c>
       <c r="R26" t="n">
-        <v>6784656</v>
+        <v>6784633</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,19 +3313,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,24 +3330,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787770</t>
+          <t>https://artportalen.se/Sighting/119787665</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119787807</v>
+        <v>119787770</v>
       </c>
       <c r="B27" t="n">
         <v>93213</v>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481250</v>
+        <v>481267</v>
       </c>
       <c r="R27" t="n">
-        <v>6784659</v>
+        <v>6784656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3453,13 +3453,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787807</t>
+          <t>https://artportalen.se/Sighting/119787770</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119787861</v>
+        <v>119787807</v>
       </c>
       <c r="B28" t="n">
         <v>93213</v>
@@ -3487,26 +3487,17 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481216</v>
+        <v>481250</v>
       </c>
       <c r="R28" t="n">
-        <v>6784655</v>
+        <v>6784659</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,13 +3565,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787861</t>
+          <t>https://artportalen.se/Sighting/119787807</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788033</v>
+        <v>119787861</v>
       </c>
       <c r="B29" t="n">
         <v>93213</v>
@@ -3608,17 +3599,26 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481181</v>
+        <v>481216</v>
       </c>
       <c r="R29" t="n">
-        <v>6784644</v>
+        <v>6784655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,9 +3648,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,24 +3675,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788033</t>
+          <t>https://artportalen.se/Sighting/119787861</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788082</v>
+        <v>119788033</v>
       </c>
       <c r="B30" t="n">
         <v>93213</v>
@@ -3717,10 +3727,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481144</v>
+        <v>481181</v>
       </c>
       <c r="R30" t="n">
-        <v>6784602</v>
+        <v>6784644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,13 +3788,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788082</t>
+          <t>https://artportalen.se/Sighting/119788033</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788715</v>
+        <v>119788082</v>
       </c>
       <c r="B31" t="n">
         <v>93213</v>
@@ -3815,14 +3825,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481104</v>
+        <v>481144</v>
       </c>
       <c r="R31" t="n">
-        <v>6784681</v>
+        <v>6784602</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,19 +3862,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3879,24 +3879,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788715</t>
+          <t>https://artportalen.se/Sighting/119788082</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788776</v>
+        <v>119788715</v>
       </c>
       <c r="B32" t="n">
         <v>93213</v>
@@ -3927,14 +3927,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481179</v>
+        <v>481104</v>
       </c>
       <c r="R32" t="n">
-        <v>6784744</v>
+        <v>6784681</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,9 +3964,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,24 +3991,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788776</t>
+          <t>https://artportalen.se/Sighting/119788715</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119789001</v>
+        <v>119788776</v>
       </c>
       <c r="B33" t="n">
         <v>93213</v>
@@ -4033,10 +4043,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481138</v>
+        <v>481179</v>
       </c>
       <c r="R33" t="n">
-        <v>6784747</v>
+        <v>6784744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,24 +4093,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119789001</t>
+          <t>https://artportalen.se/Sighting/119788776</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119789105</v>
+        <v>119789001</v>
       </c>
       <c r="B34" t="n">
         <v>93213</v>
@@ -4135,10 +4145,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481038</v>
+        <v>481138</v>
       </c>
       <c r="R34" t="n">
-        <v>6784721</v>
+        <v>6784747</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4185,49 +4195,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119789105</t>
+          <t>https://artportalen.se/Sighting/119789001</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119787325</v>
+        <v>119789105</v>
       </c>
       <c r="B35" t="n">
-        <v>87325</v>
+        <v>93213</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4237,10 +4247,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481288</v>
+        <v>481038</v>
       </c>
       <c r="R35" t="n">
-        <v>6784474</v>
+        <v>6784721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4292,22 +4302,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787325</t>
+          <t>https://artportalen.se/Sighting/119789105</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119788846</v>
+        <v>119787325</v>
       </c>
       <c r="B36" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4315,21 +4325,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4339,10 +4349,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481139</v>
+        <v>481288</v>
       </c>
       <c r="R36" t="n">
-        <v>6784744</v>
+        <v>6784474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4394,22 +4404,22 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788846</t>
+          <t>https://artportalen.se/Sighting/119787325</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119787790</v>
+        <v>119788846</v>
       </c>
       <c r="B37" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,21 +4427,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4441,10 +4451,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481260</v>
+        <v>481139</v>
       </c>
       <c r="R37" t="n">
-        <v>6784612</v>
+        <v>6784744</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,16 +4512,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787790</t>
+          <t>https://artportalen.se/Sighting/119788846</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119683440</v>
+        <v>119787790</v>
       </c>
       <c r="B38" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,45 +4529,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481045</v>
+        <v>481260</v>
       </c>
       <c r="R38" t="n">
-        <v>6784589</v>
+        <v>6784612</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4584,22 +4583,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4608,31 +4597,30 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119683440</t>
+          <t>https://artportalen.se/Sighting/119787790</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119683503</v>
+        <v>119683440</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4662,7 +4650,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4678,13 +4666,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481058</v>
+        <v>481045</v>
       </c>
       <c r="R39" t="n">
-        <v>6784561</v>
+        <v>6784589</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4713,7 +4701,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4723,7 +4711,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4750,13 +4738,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119683503</t>
+          <t>https://artportalen.se/Sighting/119683440</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119706918</v>
+        <v>119683503</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4784,20 +4772,28 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481159</v>
+        <v>481058</v>
       </c>
       <c r="R40" t="n">
-        <v>6784628</v>
+        <v>6784561</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4824,12 +4820,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4850,19 +4856,19 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706918</t>
+          <t>https://artportalen.se/Sighting/119683503</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119741905</v>
+        <v>119706918</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -4891,16 +4897,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481034</v>
+        <v>481159</v>
       </c>
       <c r="R41" t="n">
-        <v>6784535</v>
+        <v>6784628</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4927,22 +4936,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4951,6 +4950,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4962,19 +4962,19 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119741905</t>
+          <t>https://artportalen.se/Sighting/119706918</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119786992</v>
+        <v>119741905</v>
       </c>
       <c r="B42" t="n">
         <v>93197</v>
@@ -5005,17 +5005,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481048</v>
+        <v>481034</v>
       </c>
       <c r="R42" t="n">
-        <v>6784513</v>
+        <v>6784535</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5039,12 +5039,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,24 +5069,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119786992</t>
+          <t>https://artportalen.se/Sighting/119741905</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119787094</v>
+        <v>119786992</v>
       </c>
       <c r="B43" t="n">
         <v>93197</v>
@@ -5111,10 +5121,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481175</v>
+        <v>481048</v>
       </c>
       <c r="R43" t="n">
-        <v>6784516</v>
+        <v>6784513</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5161,24 +5171,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787094</t>
+          <t>https://artportalen.se/Sighting/119786992</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119787740</v>
+        <v>119787094</v>
       </c>
       <c r="B44" t="n">
         <v>93197</v>
@@ -5213,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481276</v>
+        <v>481175</v>
       </c>
       <c r="R44" t="n">
-        <v>6784646</v>
+        <v>6784516</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5263,24 +5273,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787740</t>
+          <t>https://artportalen.se/Sighting/119787094</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119787827</v>
+        <v>119787740</v>
       </c>
       <c r="B45" t="n">
         <v>93197</v>
@@ -5315,10 +5325,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481229</v>
+        <v>481276</v>
       </c>
       <c r="R45" t="n">
-        <v>6784643</v>
+        <v>6784646</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5365,24 +5375,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787827</t>
+          <t>https://artportalen.se/Sighting/119787740</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119787842</v>
+        <v>119787827</v>
       </c>
       <c r="B46" t="n">
         <v>93197</v>
@@ -5413,14 +5423,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481216</v>
+        <v>481229</v>
       </c>
       <c r="R46" t="n">
-        <v>6784655</v>
+        <v>6784643</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5450,19 +5460,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5477,24 +5477,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787842</t>
+          <t>https://artportalen.se/Sighting/119787827</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119787848</v>
+        <v>119787842</v>
       </c>
       <c r="B47" t="n">
         <v>93197</v>
@@ -5525,14 +5525,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481187</v>
+        <v>481216</v>
       </c>
       <c r="R47" t="n">
-        <v>6784640</v>
+        <v>6784655</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,9 +5562,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5579,24 +5589,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787848</t>
+          <t>https://artportalen.se/Sighting/119787842</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119788094</v>
+        <v>119787848</v>
       </c>
       <c r="B48" t="n">
         <v>93197</v>
@@ -5631,10 +5641,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481132</v>
+        <v>481187</v>
       </c>
       <c r="R48" t="n">
-        <v>6784594</v>
+        <v>6784640</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5681,24 +5691,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788094</t>
+          <t>https://artportalen.se/Sighting/119787848</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788514</v>
+        <v>119788094</v>
       </c>
       <c r="B49" t="n">
         <v>93197</v>
@@ -5733,10 +5743,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481088</v>
+        <v>481132</v>
       </c>
       <c r="R49" t="n">
-        <v>6784614</v>
+        <v>6784594</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5794,13 +5804,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788514</t>
+          <t>https://artportalen.se/Sighting/119788094</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119788519</v>
+        <v>119788514</v>
       </c>
       <c r="B50" t="n">
         <v>93197</v>
@@ -5835,10 +5845,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481087</v>
+        <v>481088</v>
       </c>
       <c r="R50" t="n">
-        <v>6784724</v>
+        <v>6784614</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5885,24 +5895,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788519</t>
+          <t>https://artportalen.se/Sighting/119788514</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119788565</v>
+        <v>119788519</v>
       </c>
       <c r="B51" t="n">
         <v>93197</v>
@@ -5937,10 +5947,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481108</v>
+        <v>481087</v>
       </c>
       <c r="R51" t="n">
-        <v>6784708</v>
+        <v>6784724</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5998,13 +6008,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788565</t>
+          <t>https://artportalen.se/Sighting/119788519</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119788662</v>
+        <v>119788565</v>
       </c>
       <c r="B52" t="n">
         <v>93197</v>
@@ -6039,10 +6049,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481133</v>
+        <v>481108</v>
       </c>
       <c r="R52" t="n">
-        <v>6784731</v>
+        <v>6784708</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6100,13 +6110,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788662</t>
+          <t>https://artportalen.se/Sighting/119788565</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119788851</v>
+        <v>119788662</v>
       </c>
       <c r="B53" t="n">
         <v>93197</v>
@@ -6137,14 +6147,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481136</v>
+        <v>481133</v>
       </c>
       <c r="R53" t="n">
-        <v>6784750</v>
+        <v>6784731</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6174,19 +6184,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6201,27 +6201,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788851</t>
+          <t>https://artportalen.se/Sighting/119788662</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119788774</v>
+        <v>119788851</v>
       </c>
       <c r="B54" t="n">
-        <v>90522</v>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6229,21 +6229,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481195</v>
+        <v>481136</v>
       </c>
       <c r="R54" t="n">
-        <v>6784739</v>
+        <v>6784750</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6324,16 +6324,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788774</t>
+          <t>https://artportalen.se/Sighting/119788851</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119788782</v>
+        <v>119788774</v>
       </c>
       <c r="B55" t="n">
-        <v>93235</v>
+        <v>90522</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,33 +6341,24 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
@@ -6445,51 +6436,60 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788782</t>
+          <t>https://artportalen.se/Sighting/119788774</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119787470</v>
+        <v>119788782</v>
       </c>
       <c r="B56" t="n">
-        <v>93181</v>
+        <v>93235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481284</v>
+        <v>481195</v>
       </c>
       <c r="R56" t="n">
-        <v>6784549</v>
+        <v>6784739</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6519,9 +6519,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6536,72 +6546,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787470</t>
+          <t>https://artportalen.se/Sighting/119788782</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119792265</v>
+        <v>119787470</v>
       </c>
       <c r="B57" t="n">
-        <v>90681</v>
+        <v>93181</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6268</v>
+        <v>6055</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481044</v>
+        <v>481284</v>
       </c>
       <c r="R57" t="n">
-        <v>6784736</v>
+        <v>6784549</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6639,81 +6642,78 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119792265</t>
+          <t>https://artportalen.se/Sighting/119787470</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119683370</v>
+        <v>119792265</v>
       </c>
       <c r="B58" t="n">
-        <v>90691</v>
+        <v>90681</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6276</v>
+        <v>6268</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481038</v>
+        <v>481044</v>
       </c>
       <c r="R58" t="n">
-        <v>6784595</v>
+        <v>6784736</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6737,22 +6737,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6761,6 +6751,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6772,19 +6763,19 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119683370</t>
+          <t>https://artportalen.se/Sighting/119792265</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119683489</v>
+        <v>119683370</v>
       </c>
       <c r="B59" t="n">
         <v>90691</v>
@@ -6812,19 +6803,26 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481045</v>
+        <v>481038</v>
       </c>
       <c r="R59" t="n">
-        <v>6784589</v>
+        <v>6784595</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6856,7 +6854,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6866,7 +6864,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6875,7 +6873,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6893,13 +6890,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119683489</t>
+          <t>https://artportalen.se/Sighting/119683370</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119706870</v>
+        <v>119683489</v>
       </c>
       <c r="B60" t="n">
         <v>90691</v>
@@ -6927,24 +6924,19 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481067</v>
+        <v>481045</v>
       </c>
       <c r="R60" t="n">
-        <v>6784504</v>
+        <v>6784589</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6971,12 +6963,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6997,19 +6999,19 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706870</t>
+          <t>https://artportalen.se/Sighting/119683489</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119706902</v>
+        <v>119706870</v>
       </c>
       <c r="B61" t="n">
         <v>90691</v>
@@ -7039,7 +7041,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -7051,10 +7053,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481174</v>
+        <v>481067</v>
       </c>
       <c r="R61" t="n">
-        <v>6784548</v>
+        <v>6784504</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7113,13 +7115,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706902</t>
+          <t>https://artportalen.se/Sighting/119706870</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119741440</v>
+        <v>119706902</v>
       </c>
       <c r="B62" t="n">
         <v>90691</v>
@@ -7147,20 +7149,27 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481034</v>
+        <v>481174</v>
       </c>
       <c r="R62" t="n">
-        <v>6784535</v>
+        <v>6784548</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7184,22 +7193,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7208,6 +7207,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7219,22 +7219,22 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119741440</t>
+          <t>https://artportalen.se/Sighting/119706902</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119788482</v>
+        <v>119741440</v>
       </c>
       <c r="B63" t="n">
-        <v>90710</v>
+        <v>90691</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7242,37 +7242,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481092</v>
+        <v>481034</v>
       </c>
       <c r="R63" t="n">
-        <v>6784610</v>
+        <v>6784535</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7296,12 +7296,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7316,24 +7326,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788482</t>
+          <t>https://artportalen.se/Sighting/119741440</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119788483</v>
+        <v>119788482</v>
       </c>
       <c r="B64" t="n">
         <v>90710</v>
@@ -7364,14 +7374,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481050</v>
+        <v>481092</v>
       </c>
       <c r="R64" t="n">
-        <v>6784604</v>
+        <v>6784610</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7401,19 +7411,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7428,27 +7428,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788483</t>
+          <t>https://artportalen.se/Sighting/119788482</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119706846</v>
+        <v>119788483</v>
       </c>
       <c r="B65" t="n">
-        <v>79327</v>
+        <v>90710</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7456,40 +7456,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481066</v>
+        <v>481050</v>
       </c>
       <c r="R65" t="n">
-        <v>6784528</v>
+        <v>6784604</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7513,12 +7510,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7527,7 +7534,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7539,19 +7545,19 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706846</t>
+          <t>https://artportalen.se/Sighting/119788483</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119706847</v>
+        <v>119706846</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7589,10 +7595,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481062</v>
+        <v>481066</v>
       </c>
       <c r="R66" t="n">
-        <v>6784508</v>
+        <v>6784528</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7651,13 +7657,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706847</t>
+          <t>https://artportalen.se/Sighting/119706846</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119706873</v>
+        <v>119706847</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -7695,10 +7701,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481067</v>
+        <v>481062</v>
       </c>
       <c r="R67" t="n">
-        <v>6784504</v>
+        <v>6784508</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7757,13 +7763,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706873</t>
+          <t>https://artportalen.se/Sighting/119706847</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119706877</v>
+        <v>119706873</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7801,7 +7807,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481065</v>
+        <v>481067</v>
       </c>
       <c r="R68" t="n">
         <v>6784504</v>
@@ -7863,13 +7869,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706877</t>
+          <t>https://artportalen.se/Sighting/119706873</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119706890</v>
+        <v>119706877</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -7907,10 +7913,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481078</v>
+        <v>481065</v>
       </c>
       <c r="R69" t="n">
-        <v>6784518</v>
+        <v>6784504</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7969,13 +7975,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706890</t>
+          <t>https://artportalen.se/Sighting/119706877</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119706923</v>
+        <v>119706890</v>
       </c>
       <c r="B70" t="n">
         <v>79327</v>
@@ -8013,10 +8019,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481092</v>
+        <v>481078</v>
       </c>
       <c r="R70" t="n">
-        <v>6784685</v>
+        <v>6784518</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8075,13 +8081,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706923</t>
+          <t>https://artportalen.se/Sighting/119706890</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119706939</v>
+        <v>119706923</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8119,10 +8125,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481111</v>
+        <v>481092</v>
       </c>
       <c r="R71" t="n">
-        <v>6784709</v>
+        <v>6784685</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8181,13 +8187,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706939</t>
+          <t>https://artportalen.se/Sighting/119706923</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119786836</v>
+        <v>119706939</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8216,19 +8222,22 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481049</v>
+        <v>481111</v>
       </c>
       <c r="R72" t="n">
-        <v>6784514</v>
+        <v>6784709</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8252,12 +8261,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8266,30 +8275,31 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119786836</t>
+          <t>https://artportalen.se/Sighting/119706939</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119787021</v>
+        <v>119786836</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8324,10 +8334,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481048</v>
+        <v>481049</v>
       </c>
       <c r="R73" t="n">
-        <v>6784513</v>
+        <v>6784514</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8374,24 +8384,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787021</t>
+          <t>https://artportalen.se/Sighting/119786836</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119787139</v>
+        <v>119787021</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8422,11 +8432,11 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481215</v>
+        <v>481048</v>
       </c>
       <c r="R74" t="n">
         <v>6784513</v>
@@ -8459,19 +8469,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8486,24 +8486,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787139</t>
+          <t>https://artportalen.se/Sighting/119787021</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119787644</v>
+        <v>119787139</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8534,14 +8534,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481277</v>
+        <v>481215</v>
       </c>
       <c r="R75" t="n">
-        <v>6784621</v>
+        <v>6784513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8571,9 +8571,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8588,24 +8598,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787644</t>
+          <t>https://artportalen.se/Sighting/119787139</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119787681</v>
+        <v>119787644</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8640,10 +8650,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481294</v>
+        <v>481277</v>
       </c>
       <c r="R76" t="n">
-        <v>6784626</v>
+        <v>6784621</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8690,24 +8700,24 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787681</t>
+          <t>https://artportalen.se/Sighting/119787644</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119787744</v>
+        <v>119787681</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8738,17 +8748,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481267</v>
+        <v>481294</v>
       </c>
       <c r="R77" t="n">
-        <v>6784656</v>
+        <v>6784626</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8775,19 +8785,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8802,24 +8802,24 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787744</t>
+          <t>https://artportalen.se/Sighting/119787681</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119787764</v>
+        <v>119787744</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8850,17 +8850,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481252</v>
+        <v>481267</v>
       </c>
       <c r="R78" t="n">
-        <v>6784627</v>
+        <v>6784656</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8887,9 +8887,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8904,24 +8914,24 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787764</t>
+          <t>https://artportalen.se/Sighting/119787744</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119787771</v>
+        <v>119787764</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8956,10 +8966,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481276</v>
+        <v>481252</v>
       </c>
       <c r="R79" t="n">
-        <v>6784646</v>
+        <v>6784627</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9006,24 +9016,24 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787771</t>
+          <t>https://artportalen.se/Sighting/119787764</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119787825</v>
+        <v>119787771</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9054,14 +9064,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481250</v>
+        <v>481276</v>
       </c>
       <c r="R80" t="n">
-        <v>6784659</v>
+        <v>6784646</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9091,19 +9101,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9118,24 +9118,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787825</t>
+          <t>https://artportalen.se/Sighting/119787771</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119787935</v>
+        <v>119787825</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9166,14 +9166,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481160</v>
+        <v>481250</v>
       </c>
       <c r="R81" t="n">
-        <v>6784611</v>
+        <v>6784659</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9203,9 +9203,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9220,24 +9230,24 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787935</t>
+          <t>https://artportalen.se/Sighting/119787825</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119788312</v>
+        <v>119787935</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9272,10 +9282,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481062</v>
+        <v>481160</v>
       </c>
       <c r="R82" t="n">
-        <v>6784614</v>
+        <v>6784611</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9333,13 +9343,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788312</t>
+          <t>https://artportalen.se/Sighting/119787935</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119788560</v>
+        <v>119788312</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9374,7 +9384,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481088</v>
+        <v>481062</v>
       </c>
       <c r="R83" t="n">
         <v>6784614</v>
@@ -9435,13 +9445,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788560</t>
+          <t>https://artportalen.se/Sighting/119788312</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788786</v>
+        <v>119788560</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9476,10 +9486,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481176</v>
+        <v>481088</v>
       </c>
       <c r="R84" t="n">
-        <v>6784737</v>
+        <v>6784614</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9537,13 +9547,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788786</t>
+          <t>https://artportalen.se/Sighting/119788560</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788928</v>
+        <v>119788786</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9578,10 +9588,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481138</v>
+        <v>481176</v>
       </c>
       <c r="R85" t="n">
-        <v>6784747</v>
+        <v>6784737</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9639,13 +9649,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788928</t>
+          <t>https://artportalen.se/Sighting/119788786</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119789077</v>
+        <v>119788928</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9680,10 +9690,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481052</v>
+        <v>481138</v>
       </c>
       <c r="R86" t="n">
-        <v>6784759</v>
+        <v>6784747</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9741,38 +9751,38 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119789077</t>
+          <t>https://artportalen.se/Sighting/119788928</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119787759</v>
+        <v>119789077</v>
       </c>
       <c r="B87" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9782,10 +9792,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481248</v>
+        <v>481052</v>
       </c>
       <c r="R87" t="n">
-        <v>6784628</v>
+        <v>6784759</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9832,71 +9842,62 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787759</t>
+          <t>https://artportalen.se/Sighting/119789077</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787544</v>
+        <v>119787759</v>
       </c>
       <c r="B88" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481291</v>
+        <v>481248</v>
       </c>
       <c r="R88" t="n">
-        <v>6784590</v>
+        <v>6784628</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9926,52 +9927,41 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119787544</t>
+          <t>https://artportalen.se/Sighting/119787759</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119788104</v>
+        <v>119787544</v>
       </c>
       <c r="B89" t="n">
         <v>8455</v>
@@ -10000,21 +9990,25 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481122</v>
+        <v>481291</v>
       </c>
       <c r="R89" t="n">
-        <v>6784602</v>
+        <v>6784590</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10044,41 +10038,52 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788104</t>
+          <t>https://artportalen.se/Sighting/119787544</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119788574</v>
+        <v>119788104</v>
       </c>
       <c r="B90" t="n">
         <v>8455</v>
@@ -10114,14 +10119,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481104</v>
+        <v>481122</v>
       </c>
       <c r="R90" t="n">
-        <v>6784681</v>
+        <v>6784602</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10151,19 +10156,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10178,72 +10173,70 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788574</t>
+          <t>https://artportalen.se/Sighting/119788104</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119706984</v>
+        <v>119788574</v>
       </c>
       <c r="B91" t="n">
-        <v>91402</v>
+        <v>8455</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>256703</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481148</v>
+        <v>481104</v>
       </c>
       <c r="R91" t="n">
-        <v>6784737</v>
+        <v>6784681</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10267,12 +10260,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10281,7 +10284,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10293,19 +10295,19 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706984</t>
+          <t>https://artportalen.se/Sighting/119788574</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119788550</v>
+        <v>119706984</v>
       </c>
       <c r="B92" t="n">
         <v>91402</v>
@@ -10335,27 +10337,25 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481050</v>
+        <v>481148</v>
       </c>
       <c r="R92" t="n">
-        <v>6784604</v>
+        <v>6784737</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10379,22 +10379,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10403,6 +10393,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10414,19 +10405,19 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119788550</t>
+          <t>https://artportalen.se/Sighting/119706984</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128635312</v>
+        <v>119788550</v>
       </c>
       <c r="B93" t="n">
         <v>91402</v>
@@ -10470,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481081</v>
+        <v>481050</v>
       </c>
       <c r="R93" t="n">
-        <v>6784713</v>
+        <v>6784604</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10500,22 +10491,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,22 +10526,22 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128635312</t>
+          <t>https://artportalen.se/Sighting/119788550</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119706843</v>
+        <v>128635312</v>
       </c>
       <c r="B94" t="n">
-        <v>79350</v>
+        <v>91402</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10558,40 +10549,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481041</v>
+        <v>481081</v>
       </c>
       <c r="R94" t="n">
-        <v>6784526</v>
+        <v>6784713</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10615,12 +10612,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10629,7 +10636,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10641,22 +10647,22 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706843</t>
+          <t>https://artportalen.se/Sighting/128635312</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119706891</v>
+        <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>79350</v>
+        <v>91544</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10664,40 +10670,46 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>260591</v>
+        <v>256703</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481078</v>
+        <v>481099</v>
       </c>
       <c r="R95" t="n">
-        <v>6784518</v>
+        <v>6784693</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10721,12 +10733,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10735,7 +10757,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10747,19 +10768,19 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706891</t>
+          <t>https://artportalen.se/Sighting/136128462</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119787824</v>
+        <v>119706843</v>
       </c>
       <c r="B96" t="n">
         <v>79350</v>
@@ -10788,19 +10809,22 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481276</v>
+        <v>481041</v>
       </c>
       <c r="R96" t="n">
-        <v>6784646</v>
+        <v>6784526</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10824,12 +10848,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10838,22 +10862,231 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706843</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>119706891</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Väster Unnån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>481078</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6784518</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706891</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>119787824</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Unnan, Unnan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>481276</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6784646</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119787824</t>
         </is>
@@ -10956,6 +11189,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91546</v>
+        <v>91552</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91553</v>
+        <v>91559</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91559</v>
+        <v>91566</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91566</v>
+        <v>91567</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91567</v>
+        <v>91580</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91580</v>
+        <v>91581</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
